--- a/productos/03_cobertura/01_tablas_informe/tabla_7.xlsx
+++ b/productos/03_cobertura/01_tablas_informe/tabla_7.xlsx
@@ -19,18 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Tomas</t>
-  </si>
-  <si>
-    <t>Total de Productos</t>
-  </si>
-  <si>
-    <t>% Productos</t>
-  </si>
-  <si>
-    <t>% Acumulado</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Cantidad de Productos</t>
+  </si>
+  <si>
+    <t>Empresas</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
   </si>
   <si>
     <t>1</t>
@@ -48,35 +45,14 @@
     <t>5</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,13 +62,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -109,7 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -138,31 +107,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -464,207 +431,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3">
+        <v>84</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.32940000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
-        <v>88</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.38769999999999999</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.38769999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="3">
+        <v>70</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.27450000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
-        <v>53</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.23350000000000001</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.62119999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="3">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.17249999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
-        <v>34</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.14979999999999999</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.77100000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="3">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2">
-        <v>16</v>
-      </c>
-      <c r="C5" s="5">
-        <v>7.0499999999999993E-2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.84150000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="3">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.1255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
-        <v>11</v>
-      </c>
-      <c r="C6" s="5">
-        <v>4.8500000000000001E-2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>3.9600000000000003E-2</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.92959999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.7600000000000001E-2</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.94720000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.9516</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.97360000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2">
-        <v>3</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1.32E-2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.98680000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0.99119999999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0.99560000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="B7" s="3">
+        <v>255</v>
+      </c>
+      <c r="C7" s="4">
         <v>1</v>
       </c>
     </row>
